--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260930.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260930.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>11.64%</t>
+          <t>11.69%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.71%</t>
+          <t>10.70%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.01%</t>
+          <t>7.99%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.76%</t>
+          <t>7.63%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.13%</t>
+          <t>5.18%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.94%</t>
+          <t>4.75%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.10%</t>
+          <t>4.14%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>3.31%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>3.27%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.93%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.32%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
@@ -1041,44 +1041,44 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>TTEK UW</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>德照科技公司</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>94,663</t>
+          <t>49,860</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>TTEK UW</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>德照科技公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>49,860</t>
+          <t>94,663</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
@@ -1276,51 +1276,51 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>EVRG US</t>
+          <t>MTZ US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Evergy公司</t>
+          <t>MasTec公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>30,114</t>
+          <t>11,237</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>MTZ US</t>
+          <t>EVRG US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>MasTec公司</t>
+          <t>Evergy公司</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>11,237</t>
+          <t>30,114</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       <c r="B72" s="3" t="inlineStr"/>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>166,489,369</t>
+          <t>166,219,998</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
